--- a/outputs/55817.xlsx
+++ b/outputs/55817.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
   <si>
     <t xml:space="preserve">QS</t>
   </si>
@@ -227,12 +227,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -488,315 +492,330 @@
   <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="9.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="str">
+        <f aca="false">A2</f>
+        <v>Question 1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="str">
+        <f aca="false">A23</f>
+        <v>Question 4</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f aca="false">A24</f>
+        <v>Option A4</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f aca="false">A25</f>
+        <v>Option B4</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f aca="false">A26</f>
+        <v>Option C4</v>
+      </c>
+      <c r="F5" s="1" t="str">
+        <f aca="false">A27</f>
+        <v>Option D4</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <f aca="false">A28</f>
+        <v>Answer 4</v>
+      </c>
+      <c r="H5" s="1" t="str">
+        <f aca="false">A29</f>
+        <v>Explanation 4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f aca="false">A30</f>
+        <v>Question 5</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f aca="false">A31</f>
+        <v>Option A5</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f aca="false">A32</f>
+        <v>Option B5</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f aca="false">A33</f>
+        <v>Option C5</v>
+      </c>
+      <c r="F6" s="1" t="str">
+        <f aca="false">A34</f>
+        <v>Option D5</v>
+      </c>
+      <c r="G6" s="1" t="str">
+        <f aca="false">A35</f>
+        <v>Answer 5</v>
+      </c>
+      <c r="H6" s="1" t="str">
+        <f aca="false">A36</f>
+        <v>Explanation 5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="0" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="0" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="0" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="0" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="0" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="0" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="0" t="s">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="0" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="0" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="0" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="0" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="0" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="0" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>41</v>
       </c>
     </row>

--- a/outputs/55817.xlsx
+++ b/outputs/55817.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t xml:space="preserve">QS</t>
   </si>
@@ -555,52 +555,66 @@
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>20</v>
+      <c r="B3" s="1" t="str">
+        <f aca="false">A2</f>
+        <v>Question 1</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f aca="false">A3</f>
+        <v>Option A1</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f aca="false">A4</f>
+        <v>Option B1</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f aca="false">A5</f>
+        <v>Option C1</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <f aca="false">A6</f>
+        <v>Option D1</v>
+      </c>
+      <c r="G3" s="1" t="str">
+        <f aca="false">A7</f>
+        <v>Answer 1</v>
+      </c>
+      <c r="H3" s="1" t="str">
+        <f aca="false">A8</f>
+        <v>Explanation 1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>27</v>
+      <c r="B4" s="1" t="str">
+        <f aca="false">A3</f>
+        <v>Option A1</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f aca="false">A4</f>
+        <v>Option B1</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f aca="false">A5</f>
+        <v>Option C1</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f aca="false">A6</f>
+        <v>Option D1</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f aca="false">A7</f>
+        <v>Answer 1</v>
+      </c>
+      <c r="G4" s="1" t="str">
+        <f aca="false">A8</f>
+        <v>Explanation 1</v>
+      </c>
+      <c r="H4" s="1" t="str">
+        <f aca="false">A9</f>
+        <v>Question 2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -608,32 +622,32 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f aca="false">A23</f>
-        <v>Question 4</v>
+        <f aca="false">A4</f>
+        <v>Option B1</v>
       </c>
       <c r="C5" s="1" t="str">
-        <f aca="false">A24</f>
-        <v>Option A4</v>
+        <f aca="false">A5</f>
+        <v>Option C1</v>
       </c>
       <c r="D5" s="1" t="str">
-        <f aca="false">A25</f>
-        <v>Option B4</v>
+        <f aca="false">A6</f>
+        <v>Option D1</v>
       </c>
       <c r="E5" s="1" t="str">
-        <f aca="false">A26</f>
-        <v>Option C4</v>
+        <f aca="false">A7</f>
+        <v>Answer 1</v>
       </c>
       <c r="F5" s="1" t="str">
-        <f aca="false">A27</f>
-        <v>Option D4</v>
+        <f aca="false">A8</f>
+        <v>Explanation 1</v>
       </c>
       <c r="G5" s="1" t="str">
-        <f aca="false">A28</f>
-        <v>Answer 4</v>
+        <f aca="false">A9</f>
+        <v>Question 2</v>
       </c>
       <c r="H5" s="1" t="str">
-        <f aca="false">A29</f>
-        <v>Explanation 4</v>
+        <f aca="false">A10</f>
+        <v>Option A2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -641,37 +655,65 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f aca="false">A30</f>
-        <v>Question 5</v>
+        <f aca="false">A5</f>
+        <v>Option C1</v>
       </c>
       <c r="C6" s="1" t="str">
-        <f aca="false">A31</f>
-        <v>Option A5</v>
+        <f aca="false">A6</f>
+        <v>Option D1</v>
       </c>
       <c r="D6" s="1" t="str">
-        <f aca="false">A32</f>
-        <v>Option B5</v>
+        <f aca="false">A7</f>
+        <v>Answer 1</v>
       </c>
       <c r="E6" s="1" t="str">
-        <f aca="false">A33</f>
-        <v>Option C5</v>
+        <f aca="false">A8</f>
+        <v>Explanation 1</v>
       </c>
       <c r="F6" s="1" t="str">
-        <f aca="false">A34</f>
-        <v>Option D5</v>
+        <f aca="false">A9</f>
+        <v>Question 2</v>
       </c>
       <c r="G6" s="1" t="str">
-        <f aca="false">A35</f>
-        <v>Answer 5</v>
+        <f aca="false">A10</f>
+        <v>Option A2</v>
       </c>
       <c r="H6" s="1" t="str">
-        <f aca="false">A36</f>
-        <v>Explanation 5</v>
+        <f aca="false">A11</f>
+        <v>Option B2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f aca="false">A6</f>
+        <v>Option D1</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f aca="false">A7</f>
+        <v>Answer 1</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f aca="false">A8</f>
+        <v>Explanation 1</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f aca="false">A9</f>
+        <v>Question 2</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f aca="false">A10</f>
+        <v>Option A2</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f aca="false">A11</f>
+        <v>Option B2</v>
+      </c>
+      <c r="H7" s="1" t="str">
+        <f aca="false">A12</f>
+        <v>Option C2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
